--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19042,7 +19060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19091,6 +19109,74 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0019</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0019 'Kvalifikace o ČNHL' (L25, parent=NODE_S1970_71_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0023</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0023 'KVAL skupina A' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0024</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0024 'KVAL skupina B' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0025</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0025 'KVAL skupina C' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -56790,6 +56876,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0019</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1970_71_0019 'Kvalifikace o ČNHL' (L25, parent=NODE_S1970_71_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0023</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1970_71_0023 'KVAL skupina A' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0024</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1970_71_0024 'KVAL skupina B' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0025</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1970_71_0025 'KVAL skupina C' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19060,7 +19060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19113,14 +19113,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S1970_71_0019</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0019 'Kvalifikace o ČNHL' (L25, parent=NODE_S1970_71_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19130,14 +19125,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1970_71_0023</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0023 'KVAL skupina A' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19147,14 +19137,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1970_71_0024</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0024 'KVAL skupina B' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19164,17 +19149,360 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1970_71_0025</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1970_71_0025 'KVAL skupina C' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -30163,7 +30491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J600"/>
+  <dimension ref="A1:J605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -30595,12 +30923,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -30763,12 +31091,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -30973,12 +31301,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -31534,12 +31862,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -31618,12 +31946,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -32342,12 +32670,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32678,12 +33006,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -32720,12 +33048,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33019,12 +33347,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -33276,12 +33604,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Litoměřice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -33617,12 +33945,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34094,12 +34422,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -37754,12 +38082,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -39225,12 +39553,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40553,12 +40881,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -41169,12 +41497,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -41884,12 +42212,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>ČZ Strakonice</t>
         </is>
       </c>
     </row>
@@ -42500,12 +42828,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Žabovřesky u Českých Budějovic = TJ Sokol Žabovřesky (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres České Budějovice, district 'České Budějovice' potvrzen). NE Brno-Žabovřesky (mestska cast Brna)! city Žabovřesky u Českých Budějovic.</t>
+          <t>Žabovřesky u Českých Budějovic = TJ Sokol Žabovřesky (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres České Budějovice, district 'České Budějovice' potvrzen). NE Brno-Žabovřesky (mestska cast Brna)! city Žabovřesky u Českých Budějovic. || TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Žabovřesky u Českých Budějovic</t>
+          <t>Artypa Holubov</t>
         </is>
       </c>
     </row>
@@ -47336,12 +47664,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -47556,12 +47884,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové.</t>
+          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové. || TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Vysokoškolská TJ Hradec</t>
+          <t>Hradec</t>
         </is>
       </c>
     </row>
@@ -50230,12 +50558,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Nová Paka</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -50314,12 +50642,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Lipnice u Trutnova = TJ Sokol Lipnice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov, district 'okres Trutnov' potvrzen v 76/77). POZOR: NE Lipnice nad Sázavou (Vysocina - znamy hrad Lipnice nL Sázavou Karla Havlicka Borovskeho), NE Lipnice u Plzně. city Lipnice u Trutnova.</t>
+          <t>Lipnice u Trutnova = TJ Sokol Lipnice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov, district 'okres Trutnov' potvrzen v 76/77). POZOR: NE Lipnice nad Sázavou (Vysocina - znamy hrad Lipnice nL Sázavou Karla Havlicka Borovskeho), NE Lipnice u Plzně. city Lipnice u Trutnova. || TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Lipnice u Trutnova</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -51137,12 +51465,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Vranov nad Dyjí</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -52753,12 +53081,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -56566,6 +56894,166 @@
       <c r="J600" t="inlineStr">
         <is>
           <t>Želeč</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0324</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0370</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0467</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0520</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0554</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56882,11 +57370,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -56931,21 +57419,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1970_71_0019</t>
+          <t>CLUB_S1970_71_0009</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1970_71_0019 'Kvalifikace o ČNHL' (L25, parent=NODE_S1970_71_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -56953,21 +57439,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1970_71_0023</t>
+          <t>CLUB_S1970_71_0013</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1970_71_0023 'KVAL skupina A' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56975,21 +57459,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1970_71_0024</t>
+          <t>CLUB_S1970_71_0018</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1970_71_0024 'KVAL skupina B' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56997,24 +57479,602 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1970_71_0025</t>
+          <t>CLUB_S1970_71_0031</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1970_71_0025 'KVAL skupina C' (L35, parent=NODE_S1970_71_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0033</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0035</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0050</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0058</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0059</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0066</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0072</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0080</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0091</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0140</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0183</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0216</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0245</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0251</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0258</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0273</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0286</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0401</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0406</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0463</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0465</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0485</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0504</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0524</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0324</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0370</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0467</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0520</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1970_71_0554</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -81990,6 +83050,11 @@
           <t>CLUB_S1969_70_0368</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
           <t>TR_S1970_71_00306</t>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19060,7 +19060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19115,7 +19115,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19127,7 +19127,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19139,7 +19139,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19151,7 +19151,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19163,7 +19163,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19175,7 +19175,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19187,7 +19187,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19199,7 +19199,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19211,7 +19211,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19223,7 +19223,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19235,7 +19235,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19247,7 +19247,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19259,7 +19259,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19271,7 +19271,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19283,7 +19283,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19295,7 +19295,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19307,7 +19307,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19319,7 +19319,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19331,178 +19331,10 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19519,7 +19351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19578,6 +19410,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19620,6 +19457,11 @@
           <t>10 týmů + playoff (semifinále, o 3.místo, finále). Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19667,6 +19509,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19709,6 +19556,11 @@
           <t>ČNHL: skupina A (16 CZ) a skupina B (14 SM). SNHL: základní část (12 SVK) → skupina A (1.–6.) a skupina B (7.–12.).</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19840,6 +19692,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19882,6 +19739,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19924,6 +19786,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20092,6 +19959,11 @@
           <t>Divize: 6 skupin CZ (A-F) + 2 skupiny SVK + kvalifikace o I.ČNHL.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20134,6 +20006,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0011</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20176,6 +20053,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0012</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20218,6 +20100,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0013</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20260,6 +20147,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0014</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20307,6 +20199,11 @@
           <t>Rozhodující utkání o vítěze skupiny E a postup do ČNHL: Prostějov – Dynamo Jihlava 8:4 (hráno v Gottwaldově).</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0015</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20349,6 +20246,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0016</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20396,6 +20298,11 @@
           <t>TJ Prostějov postoupil do ČNHL přímo. TJ Sigma MŽ Olomouc se přímého postupu do ČNHL vzdala.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0017</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20438,6 +20345,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0018</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20480,6 +20392,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0019</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20700,6 +20617,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20868,6 +20790,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0026</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -20910,6 +20837,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0027</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -20952,6 +20884,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0028</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -20994,6 +20931,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0029</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -21036,6 +20978,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0030</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -21120,6 +21067,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0032</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21162,6 +21114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0033</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21204,6 +21161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0034</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21246,6 +21208,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0028</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21288,6 +21255,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21545,6 +21517,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -21587,6 +21564,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -21629,6 +21611,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0044</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21671,6 +21658,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0045</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21713,6 +21705,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0046</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -21849,6 +21846,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0048</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -21891,6 +21893,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0049</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21933,6 +21940,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0050</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21975,6 +21987,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0051</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22017,6 +22034,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0052</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22101,6 +22123,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -22143,6 +22170,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0055</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22185,6 +22217,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0056</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22274,6 +22311,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0057</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22321,6 +22363,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0058</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22363,6 +22410,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0059</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22405,6 +22457,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0060</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22447,6 +22504,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0061</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22489,6 +22551,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0062</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22531,6 +22598,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0063</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22573,6 +22645,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0064</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22615,6 +22692,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0065</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22788,6 +22870,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0066</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22830,6 +22917,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0067</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -22872,6 +22964,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0068</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -22914,6 +23011,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0069</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -22956,6 +23058,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0070</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -22998,6 +23105,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0071</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23040,6 +23152,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0072</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23082,6 +23199,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0073</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23124,6 +23246,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0074</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23171,6 +23298,11 @@
           <t>kvalifikace o krajský přebor</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0075</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23218,6 +23350,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0076</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23260,6 +23397,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0079</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23302,6 +23444,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0080</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23727,6 +23874,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0088</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23769,6 +23921,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0089</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23853,6 +24010,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0090</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23895,6 +24057,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0091</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -23937,6 +24104,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0092</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -23979,6 +24151,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0093</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -24019,6 +24196,11 @@
       <c r="J105" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0094</t>
         </is>
       </c>
     </row>
@@ -30923,12 +31105,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -31091,12 +31273,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -31301,12 +31483,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -31862,12 +32044,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -31946,12 +32128,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -32670,12 +32852,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -33604,12 +33786,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -42212,12 +42394,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>ČZ Strakonice</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -42828,12 +43010,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Žabovřesky u Českých Budějovic = TJ Sokol Žabovřesky (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres České Budějovice, district 'České Budějovice' potvrzen). NE Brno-Žabovřesky (mestska cast Brna)! city Žabovřesky u Českých Budějovic. || TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Žabovřesky u Českých Budějovic = TJ Sokol Žabovřesky (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres České Budějovice, district 'České Budějovice' potvrzen). NE Brno-Žabovřesky (mestska cast Brna)! city Žabovřesky u Českých Budějovic.</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Artypa Holubov</t>
+          <t>Žabovřesky u Českých Budějovic</t>
         </is>
       </c>
     </row>
@@ -47664,12 +47846,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -50558,12 +50740,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -50642,12 +50824,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Lipnice u Trutnova = TJ Sokol Lipnice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov, district 'okres Trutnov' potvrzen v 76/77). POZOR: NE Lipnice nad Sázavou (Vysocina - znamy hrad Lipnice nL Sázavou Karla Havlicka Borovskeho), NE Lipnice u Plzně. city Lipnice u Trutnova. || TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Lipnice u Trutnova = TJ Sokol Lipnice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov, district 'okres Trutnov' potvrzen v 76/77). POZOR: NE Lipnice nad Sázavou (Vysocina - znamy hrad Lipnice nL Sázavou Karla Havlicka Borovskeho), NE Lipnice u Plzně. city Lipnice u Trutnova.</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Nová Paka</t>
+          <t>Lipnice u Trutnova</t>
         </is>
       </c>
     </row>
@@ -51465,12 +51647,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Rudá Hvězda</t>
+          <t>Vranov nad Dyjí</t>
         </is>
       </c>
     </row>
@@ -53081,12 +53263,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -57370,7 +57552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57424,12 +57606,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0009</t>
+          <t>CLUB_S1970_71_0035</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -57444,12 +57626,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0013</t>
+          <t>CLUB_S1970_71_0058</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57464,12 +57646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0018</t>
+          <t>CLUB_S1970_71_0059</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57484,12 +57666,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0031</t>
+          <t>CLUB_S1970_71_0066</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57504,12 +57686,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0033</t>
+          <t>CLUB_S1970_71_0080</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57524,12 +57706,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0035</t>
+          <t>CLUB_S1970_71_0091</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57544,12 +57726,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0050</t>
+          <t>CLUB_S1970_71_0140</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57564,12 +57746,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0058</t>
+          <t>CLUB_S1970_71_0183</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57584,12 +57766,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0059</t>
+          <t>CLUB_S1970_71_0216</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57604,12 +57786,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0066</t>
+          <t>CLUB_S1970_71_0245</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57624,12 +57806,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0072</t>
+          <t>CLUB_S1970_71_0251</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -57644,12 +57826,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0080</t>
+          <t>CLUB_S1970_71_0258</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57664,12 +57846,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0091</t>
+          <t>CLUB_S1970_71_0406</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57684,12 +57866,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0140</t>
+          <t>CLUB_S1970_71_0504</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57704,12 +57886,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0183</t>
+          <t>CLUB_S1970_71_0324</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57724,12 +57906,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0216</t>
+          <t>CLUB_S1970_71_0370</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57744,12 +57926,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0245</t>
+          <t>CLUB_S1970_71_0467</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57764,12 +57946,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0251</t>
+          <t>CLUB_S1970_71_0520</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57784,297 +57966,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0258</t>
+          <t>CLUB_S1970_71_0554</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0273</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'ČZ Strakonice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0286</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žabovřesky u Českých Budějovic' → 'Artypa Holubov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0401</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0406</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0463</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0465</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Lipnice u Trutnova' → 'Nová Paka' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0485</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0504</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0524</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0324</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0370</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0467</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0520</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1970_71_0554</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F34"/>
+  <autoFilter ref="A1:F20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Krajská soutěž / skupina D / Sokol Dolany — odstoupily, hrály OP</t>
+          <t>Krajská soutěž / skupina D</t>
         </is>
       </c>
       <c r="C47" s="2" t="n"/>
@@ -19060,7 +19060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19113,21 +19113,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[club-fate] Sokol Dolany — odstoupily, hrály OP (club_id: CLUB_S1970_71_0435)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19139,7 +19144,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19151,7 +19156,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19163,7 +19168,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19175,7 +19180,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19187,7 +19192,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19199,7 +19204,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1969_70_0440 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19211,7 +19216,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19223,7 +19228,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19235,7 +19240,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19247,7 +19252,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19259,7 +19264,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19271,7 +19276,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19283,7 +19288,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'Sokol Dolany — odstoupily, hrály OP' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19295,7 +19300,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19335,6 +19340,30 @@
         </is>
       </c>
       <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -49429,7 +49458,7 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Dolany u Pardubic = TJ Sokol Dolany (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Pardubice). city Dolany u Pardubic.</t>
+          <t>Dolany u Pardubic = TJ Sokol Dolany (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Pardubice). city Dolany u Pardubic. || TBD: extrahováno z block_name: 'Sokol Dolany — odstoupily, hrály OP' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -57552,7 +57581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57866,12 +57895,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0504</t>
+          <t>CLUB_S1970_71_0435</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: extrahováno z block_name: 'Sokol Dolany — odstoupily, hrály OP' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -57886,12 +57915,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0324</t>
+          <t>CLUB_S1970_71_0504</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57906,7 +57935,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0370</t>
+          <t>CLUB_S1970_71_0324</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -57926,7 +57955,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0467</t>
+          <t>CLUB_S1970_71_0370</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -57946,7 +57975,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1970_71_0520</t>
+          <t>CLUB_S1970_71_0467</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -57966,17 +57995,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CLUB_S1970_71_0520</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>CLUB_S1970_71_0554</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F20"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -28774,7 +28774,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M40" t="n">
         <v>22</v>
@@ -30077,7 +30077,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M53" t="n">
         <v>30</v>
@@ -30147,7 +30147,7 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -19380,7 +19380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19442,6 +19442,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -19721,6 +19721,16 @@
           <t>NODE_S1970_71_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19735,6 +19745,14 @@
         <is>
           <t>NODE_S1969_70_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -19768,6 +19786,8 @@
           <t>NODE_S1970_71_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19782,6 +19802,14 @@
         <is>
           <t>NODE_S1969_70_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -19815,6 +19843,8 @@
           <t>NODE_S1970_71_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19829,6 +19859,14 @@
         <is>
           <t>NODE_S1969_70_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21007,6 +21045,8 @@
           <t>NODE_S1970_71_0030</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21021,6 +21061,14 @@
         <is>
           <t>NODE_S1969_70_0030</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -22063,6 +22111,8 @@
           <t>NODE_S1970_71_0053</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22077,6 +22127,14 @@
         <is>
           <t>NODE_S1969_70_0052</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -22434,6 +22492,12 @@
           <t>REG_SEC</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0073</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22453,6 +22517,14 @@
         <is>
           <t>NODE_S1969_70_0059</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -22815,6 +22887,12 @@
           <t>NODE_S1970_71_0065</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0074</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22824,6 +22902,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -22857,6 +22943,8 @@
           <t>NODE_S1970_71_0065</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22866,6 +22954,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -23087,6 +23183,8 @@
           <t>NODE_S1970_71_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23101,6 +23199,14 @@
         <is>
           <t>NODE_S1969_70_0070</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -23651,6 +23757,8 @@
           <t>NODE_S1970_71_0086</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23660,6 +23768,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -24227,6 +24343,8 @@
           <t>NODE_S1970_71_0100</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24241,6 +24359,14 @@
         <is>
           <t>NODE_S1969_70_0094</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="106">

--- a/data/S1970_71_FINAL.xlsx
+++ b/data/S1970_71_FINAL.xlsx
@@ -798,6 +798,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
@@ -19786,8 +19791,6 @@
           <t>NODE_S1970_71_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19843,8 +19846,6 @@
           <t>NODE_S1970_71_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21045,8 +21046,6 @@
           <t>NODE_S1970_71_0030</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22111,8 +22110,6 @@
           <t>NODE_S1970_71_0053</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22497,7 +22494,6 @@
           <t>NODE_S1970_71_0073</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22892,7 +22888,6 @@
           <t>NODE_S1970_71_0074</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22943,8 +22938,6 @@
           <t>NODE_S1970_71_0065</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23183,8 +23176,6 @@
           <t>NODE_S1970_71_0075</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23757,8 +23748,6 @@
           <t>NODE_S1970_71_0086</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24343,8 +24332,6 @@
           <t>NODE_S1970_71_0100</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -57415,7 +57402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57703,6 +57690,18 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>Lokální rozpor Divize skupina A je uzavřen podle PDF; Jiskra Vír v 30_Jihomoravský opravena na 8–0–3 dle uživatelského upřesnění.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>
